--- a/artfynd/A 46004-2023 artfynd.xlsx
+++ b/artfynd/A 46004-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46004-2023 artfynd.xlsx
+++ b/artfynd/A 46004-2023 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>121128601</v>
       </c>
       <c r="B17" t="n">
-        <v>91370</v>
+        <v>91380</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>121329983</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 46004-2023 artfynd.xlsx
+++ b/artfynd/A 46004-2023 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>121128601</v>
       </c>
       <c r="B17" t="n">
-        <v>91380</v>
+        <v>91392</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>121329983</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 46004-2023 artfynd.xlsx
+++ b/artfynd/A 46004-2023 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>121128601</v>
       </c>
       <c r="B17" t="n">
-        <v>91392</v>
+        <v>91393</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>121329983</v>
       </c>
       <c r="B18" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 46004-2023 artfynd.xlsx
+++ b/artfynd/A 46004-2023 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>121128601</v>
       </c>
       <c r="B17" t="n">
-        <v>91393</v>
+        <v>91396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>121329983</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 46004-2023 artfynd.xlsx
+++ b/artfynd/A 46004-2023 artfynd.xlsx
@@ -2467,7 +2467,7 @@
         <v>121329983</v>
       </c>
       <c r="B18" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 46004-2023 artfynd.xlsx
+++ b/artfynd/A 46004-2023 artfynd.xlsx
@@ -2467,7 +2467,7 @@
         <v>121329983</v>
       </c>
       <c r="B18" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 46004-2023 artfynd.xlsx
+++ b/artfynd/A 46004-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2210154</v>
+        <v>121128601</v>
       </c>
       <c r="B2" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ÖOV TORSVIKEN (10J8c08), Upl</t>
+          <t>Gällnö, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>706801.6817775345</v>
+        <v>706749</v>
       </c>
       <c r="R2" t="n">
-        <v>6590996.267278629</v>
+        <v>6590967</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1998-05-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1998-05-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>100982081 / SANI EUR / Enstaka-sparsam (1)  / OBJ.AREA:0,5 ha</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,37 +757,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulf Birgersson</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Skogsstyrelsens naturvärdesobjekt</t>
+          <t>Svampar i Roslagen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116474285</v>
+        <v>116531240</v>
       </c>
       <c r="B3" t="n">
-        <v>57426</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,49 +791,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Getudden, Gällnö skärgård, Upl</t>
+          <t>Getudden, Gällnö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>706390</v>
+        <v>706380</v>
       </c>
       <c r="R3" t="n">
-        <v>6590562</v>
+        <v>6590602</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,59 +851,40 @@
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Läte hörd.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Tranberg</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Tranberg</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116438662</v>
+        <v>116531287</v>
       </c>
       <c r="B4" t="n">
-        <v>5479</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,39 +892,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101410</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>V Gustavsberg, Gällnö, Upl</t>
+          <t>Getudden, Gällnö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>706417</v>
+        <v>706393</v>
       </c>
       <c r="R4" t="n">
-        <v>6590533</v>
+        <v>6590746</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1032,15 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116438314</v>
+        <v>116531523</v>
       </c>
       <c r="B5" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,39 +993,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>V Gustavsberg, Gällnö, Upl</t>
+          <t>Getudden, Gällnö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>706417</v>
+        <v>706393</v>
       </c>
       <c r="R5" t="n">
-        <v>6590533</v>
+        <v>6590826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,6 +1064,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1139,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116531655</v>
+        <v>116531584</v>
       </c>
       <c r="B6" t="n">
-        <v>90462</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>706452</v>
+        <v>706387</v>
       </c>
       <c r="R6" t="n">
-        <v>6590866</v>
+        <v>6590848</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,43 +1184,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116531710</v>
+        <v>116531655</v>
       </c>
       <c r="B7" t="n">
-        <v>100026</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1289,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>706451</v>
+        <v>706452</v>
       </c>
       <c r="R7" t="n">
-        <v>6590939</v>
+        <v>6590866</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,53 +1285,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116531240</v>
+        <v>116438314</v>
       </c>
       <c r="B8" t="n">
-        <v>90462</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getudden, Gällnö, Upl</t>
+          <t>V Gustavsberg, Gällnö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>706380</v>
+        <v>706417</v>
       </c>
       <c r="R8" t="n">
-        <v>6590602</v>
+        <v>6590533</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1369,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,15 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116531632</v>
+        <v>116531325</v>
       </c>
       <c r="B9" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,21 +1398,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,7 +1421,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1507,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>706445</v>
+        <v>706405</v>
       </c>
       <c r="R9" t="n">
-        <v>6590843</v>
+        <v>6590795</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,51 +1494,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116531746</v>
+        <v>116531309</v>
       </c>
       <c r="B10" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>706417</v>
+        <v>706408</v>
       </c>
       <c r="R10" t="n">
-        <v>6590837</v>
+        <v>6590794</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,15 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116531523</v>
+        <v>116438662</v>
       </c>
       <c r="B11" t="n">
-        <v>90462</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,37 +1612,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>101410</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Getudden, Gällnö, Upl</t>
+          <t>V Gustavsberg, Gällnö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>706393</v>
+        <v>706417</v>
       </c>
       <c r="R11" t="n">
-        <v>6590826</v>
+        <v>6590533</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,7 +1685,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1791,51 +1703,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116531476</v>
+        <v>116531677</v>
       </c>
       <c r="B12" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1843,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>706387</v>
+        <v>706483</v>
       </c>
       <c r="R12" t="n">
-        <v>6590809</v>
+        <v>6590895</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,15 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116531677</v>
+        <v>116531864</v>
       </c>
       <c r="B13" t="n">
-        <v>5479</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>706483</v>
+        <v>706412</v>
       </c>
       <c r="R13" t="n">
-        <v>6590895</v>
+        <v>6590874</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,12 +1920,7 @@
         <v>116531510</v>
       </c>
       <c r="B14" t="n">
-        <v>4769</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,62 +2024,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116531325</v>
+        <v>116474285</v>
       </c>
       <c r="B15" t="n">
-        <v>4763</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Getudden, Gällnö, Upl</t>
+          <t>Getudden, Gällnö skärgård, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>706405</v>
+        <v>706390</v>
       </c>
       <c r="R15" t="n">
-        <v>6590795</v>
+        <v>6590562</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2212,76 +2104,88 @@
           <t>2024-05-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-05-01</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Läte hörd.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Anders Tranberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Anders Tranberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116531309</v>
+        <v>116535574</v>
       </c>
       <c r="B16" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2291,13 +2195,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>706408</v>
+        <v>706399</v>
       </c>
       <c r="R16" t="n">
-        <v>6590794</v>
+        <v>6590784</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2335,7 +2239,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2354,15 +2257,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121128601</v>
+        <v>116531632</v>
       </c>
       <c r="B17" t="n">
-        <v>91396</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,40 +2268,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gällnö, Upl</t>
+          <t>Getudden, Gällnö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>706749</v>
+        <v>706445</v>
       </c>
       <c r="R17" t="n">
-        <v>6590967</v>
+        <v>6590843</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2427,12 +2331,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,81 +2352,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121329983</v>
+        <v>2210154</v>
       </c>
       <c r="B18" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Getudden, Gällnö (*knärot* /stjälk/), Upl</t>
+          <t>ÖOV TORSVIKEN (10J8c08), Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706406</v>
+        <v>706802</v>
       </c>
       <c r="R18" t="n">
-        <v>6590824</v>
+        <v>6590996</v>
       </c>
       <c r="S18" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2544,19 +2427,19 @@
           <t>Värmdö</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>AB-Vär-0416</t>
-        </is>
-      </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>1998-05-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>1998-05-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>100982081 / SANI EUR / Enstaka-sparsam (1)  / OBJ.AREA:0,5 ha</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,26 +2448,568 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulf Birgersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>61664247</v>
+      </c>
+      <c r="B19" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gällnö, Torsviken, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>706728</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6591080</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Brynmiljö skog/gräsmark</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>116531476</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Getudden, Gällnö, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>706387</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6590809</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>116531746</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Getudden, Gällnö, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>706417</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6590837</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121329983</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Getudden, Gällnö (*knärot* /stjälk/), Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>706406</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6590824</v>
+      </c>
+      <c r="S22" t="n">
+        <v>49</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>AB-Vär-0416</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Jakob Nygren</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
+      <c r="AY22" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>116531710</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Getudden, Gällnö, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>706451</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6590939</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Värmdö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46004-2023 artfynd.xlsx
+++ b/artfynd/A 46004-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121128601</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531240</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531287</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531523</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531584</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531655</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116438314</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531325</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531309</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116438662</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1807,6 +1862,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531677</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1914,6 +1974,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531864</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2021,6 +2086,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531510</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2145,6 +2215,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116474285</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2254,6 +2329,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116535574</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2361,6 +2441,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531632</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2210154</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2569,6 +2659,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61664247</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2679,6 +2774,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531476</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2789,6 +2889,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531746</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2906,6 +3011,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121329983</t>
         </is>
       </c>
     </row>
@@ -3010,8 +3120,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116531710</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>